--- a/src/attributions/attributions_ig_traj_461.xlsx
+++ b/src/attributions/attributions_ig_traj_461.xlsx
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1816118123677879</v>
+        <v>0.044915198145799</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1011,25 +1011,25 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.008971160849015577</v>
+        <v>-0.01728965633541807</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06622123257660895</v>
+        <v>-0.01475248156720109</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2388488685395606</v>
+        <v>0.1151297390826576</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.03387585171200268</v>
+        <v>-0.05344062920846689</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1047,16 +1047,16 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1739274269504085</v>
+        <v>-0.02702474051761754</v>
       </c>
       <c r="S2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.08207926619319912</v>
+        <v>0.01879200405619628</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
@@ -1065,52 +1065,52 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01488449213085515</v>
+        <v>-0.0289602370879111</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.01556085692234375</v>
+        <v>-0.007390714323526268</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.07003987834066619</v>
+        <v>-0.03485533078409053</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.08537159619740835</v>
+        <v>-0.04861781393051653</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.004533030059460165</v>
+        <v>0.01795817932975903</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.05209229389396414</v>
+        <v>0.02695622477649708</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -1119,34 +1119,34 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.06129650037999111</v>
+        <v>0.0009191110391130082</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.04066738366142107</v>
+        <v>-0.001529096424802595</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.4142852264786511</v>
+        <v>0.1458024578380151</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.2039206375235923</v>
+        <v>-0.02709250734325999</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -1155,16 +1155,16 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.09003511548234532</v>
+        <v>-0.005386432992068339</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.005167538406497763</v>
+        <v>-0.009924349632601786</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -1173,118 +1173,118 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.04532541039124875</v>
+        <v>-0.01726131941684976</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0.06956387874833801</v>
+        <v>-0.02034288026812845</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.0122653260070152</v>
+        <v>0.01764260982827808</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
         <v>-0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.2118192311876466</v>
+        <v>0.05850234003372332</v>
       </c>
       <c r="BQ2" t="n">
         <v>-0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.06465433692098892</v>
+        <v>0.02201014854084809</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.231881399721986</v>
+        <v>0.07379393017979199</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX2" t="n">
         <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.0421490541407675</v>
+        <v>-0.02169077411211261</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
         <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.01469726276608578</v>
+        <v>-0.02135890782340959</v>
       </c>
       <c r="CD2" t="n">
         <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.08503246934443796</v>
+        <v>-0.03396407524236516</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
         <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.008462111312815391</v>
+        <v>0.01356697392949679</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.07388177817483498</v>
+        <v>0.01810380480023942</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.01363350754015975</v>
+        <v>-0.03358112910368426</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.07223360143889172</v>
+        <v>0.008018222454180777</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
@@ -1293,67 +1293,67 @@
         <v>-0</v>
       </c>
       <c r="CU2" t="n">
-        <v>-0.003336584852491956</v>
+        <v>0.01541845033990132</v>
       </c>
       <c r="CV2" t="n">
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.0893669576858795</v>
+        <v>-0.03475161606095175</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
         <v>0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.01083585811035206</v>
+        <v>0.007116904104607573</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.05259673430570867</v>
+        <v>0.01984796332457917</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.1353091199769822</v>
+        <v>-0.06884941355440299</v>
       </c>
       <c r="DG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.07026383818103829</v>
+        <v>-0.00382806595698087</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.03508351778180755</v>
+        <v>0.0008774390038514177</v>
       </c>
       <c r="DN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.02756516248829915</v>
+        <v>-0.01410860599488502</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
@@ -1362,25 +1362,25 @@
         <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.06174165309573929</v>
+        <v>0.0181380696300051</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0.02041212436926091</v>
+        <v>0.01947480065160459</v>
       </c>
       <c r="DW2" t="n">
         <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.1784034462380596</v>
+        <v>-0.02412507690880945</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
@@ -1389,10 +1389,10 @@
         <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.003911349772598811</v>
+        <v>-0.02453848256575423</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
@@ -1401,22 +1401,22 @@
         <v>-0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0.03090759262664351</v>
+        <v>0.003180947124923316</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.04821544259998597</v>
+        <v>-0.02138727887187008</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI2" t="n">
         <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.03580433211111114</v>
+        <v>-0.004367853065828535</v>
       </c>
       <c r="EK2" t="n">
         <v>-0</v>
@@ -1425,70 +1425,70 @@
         <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.109557097581434</v>
+        <v>0.01303758951402024</v>
       </c>
       <c r="EO2" t="n">
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.05411622552350438</v>
+        <v>-0.01373069972759435</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
         <v>-0</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.03576089583878649</v>
+        <v>0.01746291150560624</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
         <v>-0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.06195600393266686</v>
+        <v>0.02308394067814829</v>
       </c>
       <c r="EX2" t="n">
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.09594483267549388</v>
+        <v>-0.04574877994900097</v>
       </c>
       <c r="EZ2" t="n">
         <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.00593440283610607</v>
+        <v>0.00592455237626027</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.0495195531523307</v>
+        <v>0.01831765665874713</v>
       </c>
       <c r="FG2" t="n">
         <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.02071437508056901</v>
+        <v>0.03345933001310024</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
@@ -1497,10 +1497,10 @@
         <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.05087263747160127</v>
+        <v>-0.004755438819108486</v>
       </c>
       <c r="FL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM2" t="n">
         <v>0</v>
@@ -1509,13 +1509,13 @@
         <v>0</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.005621655468757766</v>
+        <v>0.02976826480590799</v>
       </c>
       <c r="FP2" t="n">
         <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.002646909035361061</v>
+        <v>-0.01031868628025011</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
@@ -1524,25 +1524,25 @@
         <v>-0</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.00449708203870717</v>
+        <v>0.009610081937867851</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0.04492909440631886</v>
+        <v>0.006169072322028919</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.08219587385019794</v>
+        <v>-0.02441907777970764</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
@@ -1551,19 +1551,19 @@
         <v>-0</v>
       </c>
       <c r="GC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF2" t="n">
         <v>-0</v>
       </c>
       <c r="GG2" t="n">
-        <v>-0.04333640168608897</v>
+        <v>-0.009578312647749884</v>
       </c>
     </row>
     <row r="3">
@@ -2706,25 +2706,25 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1262510535862631</v>
+        <v>0.002264287630953412</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01696167826590809</v>
+        <v>-0.001303455117704541</v>
       </c>
       <c r="F5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.109227115832669</v>
+        <v>-0.001655430181843193</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2736,25 +2736,25 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1309350771853325</v>
+        <v>0.00666586995498861</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.03443451634610976</v>
+        <v>-0.002140931864040305</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1566713096834913</v>
+        <v>-0.0050130678593814</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -2763,88 +2763,88 @@
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.07878493506336898</v>
+        <v>-0.0001582233105015863</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1944426731467038</v>
+        <v>-0.002474838330228725</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.09626842339764434</v>
+        <v>0.0002763124239925363</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1230583065680214</v>
+        <v>-0.003023029129101744</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.06309411125375507</v>
+        <v>-0.004143290500325804</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.03084374328797608</v>
+        <v>7.505798997393868e-05</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.02202373316597235</v>
+        <v>-0.0001469354325979043</v>
       </c>
       <c r="AM5" t="n">
         <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.02505212132643837</v>
+        <v>-0.0006961932689746664</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.03952379497557176</v>
+        <v>0.0002738133559754334</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.241125566741312</v>
+        <v>0.00839102418702397</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
@@ -2853,13 +2853,13 @@
         <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.140778484499566</v>
+        <v>0.0003086694179268502</v>
       </c>
       <c r="AY5" t="n">
         <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.2205091761694899</v>
+        <v>-0.000638535486789617</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2868,10 +2868,10 @@
         <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0291782764981573</v>
+        <v>-0.001174486937729588</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,13 +2880,13 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.02872233271380907</v>
+        <v>-0.001016976875968421</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.01641561536661126</v>
+        <v>-0.0004378632808218962</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
@@ -2898,22 +2898,22 @@
         <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.0002144296732009935</v>
+        <v>0.00203396529162474</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1603377952295417</v>
+        <v>0.004882379702160673</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.07114935421613679</v>
+        <v>-0.0004427407016136435</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2922,52 +2922,52 @@
         <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.08209443621780294</v>
+        <v>0.004265508693336946</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.1188089401955444</v>
+        <v>-0.0001756990278770513</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.1224912516870273</v>
+        <v>-0.0007066272448635725</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.05992915761416059</v>
+        <v>-0.001034517016694308</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG5" t="n">
         <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.03096079943596695</v>
+        <v>0.001120155258918261</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.04113536106347546</v>
+        <v>0.0007393913022696703</v>
       </c>
       <c r="CK5" t="n">
         <v>-0</v>
@@ -2976,25 +2976,25 @@
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.08206244041965999</v>
+        <v>-0.002185372050699947</v>
       </c>
       <c r="CO5" t="n">
         <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.04220223261178307</v>
+        <v>-0.0004551421968509808</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.05487697016303376</v>
+        <v>-0.0012083850188533</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
@@ -3003,25 +3003,25 @@
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.03944880868741357</v>
+        <v>-0.001072402558099668</v>
       </c>
       <c r="CX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY5" t="n">
         <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01411090062751609</v>
+        <v>0.000485811421556996</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.04887285090513219</v>
+        <v>0.001228891149808814</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.07796460123791268</v>
+        <v>-0.002730039940474748</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
@@ -3042,25 +3042,25 @@
         <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.02960082966678804</v>
+        <v>-0.002296010765740136</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.03087557600887752</v>
+        <v>0.0004711166396044274</v>
       </c>
       <c r="DL5" t="n">
         <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.02440882727941355</v>
+        <v>0.0003767389884049247</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
@@ -3069,40 +3069,40 @@
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.02238777825180803</v>
+        <v>0.0008884993694119651</v>
       </c>
       <c r="DS5" t="n">
         <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.02658845120364235</v>
+        <v>0.0017632213218617</v>
       </c>
       <c r="DU5" t="n">
         <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.1478390250858153</v>
+        <v>-0.001151788875049898</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ5" t="n">
         <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.01256529868281661</v>
+        <v>-0.0007358519820819356</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.03392567714725807</v>
+        <v>0.00249732515608663</v>
       </c>
       <c r="ED5" t="n">
         <v>-0</v>
@@ -3114,25 +3114,25 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.01872956235901924</v>
+        <v>-0.0005513442833315032</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.03423260945404685</v>
+        <v>0.0003351682548866134</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.0622642695472763</v>
+        <v>2.132545593962022e-05</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
@@ -3141,49 +3141,49 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.03349999339743496</v>
+        <v>-0.0006554124925688933</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
         <v>-0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.004006028253440358</v>
+        <v>-0.0001048110338683134</v>
       </c>
       <c r="ET5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.01212027520140182</v>
+        <v>0.0006663335491806169</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.05277241359032947</v>
+        <v>-0.001678923120757754</v>
       </c>
       <c r="EZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA5" t="n">
         <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.02933621791350726</v>
+        <v>0.0002626998483524212</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.03874072374633281</v>
+        <v>0.0008497897198010881</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
@@ -3192,64 +3192,64 @@
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.06218538781610873</v>
+        <v>0.001659713100960313</v>
       </c>
       <c r="FI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.002589342603149922</v>
+        <v>-0.001219733122192623</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.04114376033323494</v>
+        <v>-0.001419539981770081</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.006275112356073922</v>
+        <v>-2.013700026792119e-05</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.008745164324567799</v>
+        <v>0.0002021805490356748</v>
       </c>
       <c r="FU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.02128369941709869</v>
+        <v>0.001835612190180481</v>
       </c>
       <c r="FW5" t="n">
         <v>-0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.06586812633052286</v>
+        <v>-0.0008014313360757008</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
@@ -3258,13 +3258,13 @@
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.1828623923346668</v>
+        <v>0.002378071345265292</v>
       </c>
       <c r="GF5" t="n">
         <v>-0</v>
@@ -3847,22 +3847,22 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.3561938788713459</v>
+        <v>0.3014025492956817</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2093648612788099</v>
+        <v>-0.3264500690825406</v>
       </c>
       <c r="E7" t="n">
-        <v>0.006491830645778895</v>
+        <v>-0.02020278900853406</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -3874,16 +3874,16 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3425863317026235</v>
+        <v>0.4387175452449431</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2420623144133599</v>
+        <v>-0.4168346780453756</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.01782361371406201</v>
+        <v>-0.08945519003910606</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3898,25 +3898,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1698095852667296</v>
+        <v>0.1886504651049518</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.003678355541903125</v>
+        <v>-0.04380329614751088</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1241535048226961</v>
+        <v>-0.04124489989819111</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -3925,55 +3925,55 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.09105722622360875</v>
+        <v>-0.1364474360772341</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.009042153968061746</v>
+        <v>-0.2085128202573269</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.0570805785176987</v>
+        <v>-0.18606029391529</v>
       </c>
       <c r="AG7" t="n">
         <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.00822410143930849</v>
+        <v>0.2415835015572167</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.1214308954552848</v>
+        <v>-0.09082160660898239</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.0531769406314152</v>
+        <v>0.1476563969168528</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
@@ -3982,43 +3982,43 @@
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.4400818224139125</v>
+        <v>0.4188829264799736</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.0418436786970461</v>
+        <v>-0.245965435985613</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.2252480424063985</v>
+        <v>-0.2428211181766114</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.02411106473710842</v>
+        <v>-0.05481794817922672</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.05317392412254936</v>
+        <v>-0.09985517999110528</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.06740018726236219</v>
+        <v>-0.055886947356425</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4033,79 +4033,79 @@
         <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.03015371605402557</v>
+        <v>-0.08516478183923601</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.05244598734308074</v>
+        <v>0.1236468001184156</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1829743356220767</v>
+        <v>-0.04543016218961378</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.2058016086335462</v>
+        <v>0.4598283518795024</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.02579478802984657</v>
+        <v>-0.1891873181529939</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.1318752601863181</v>
+        <v>-0.04895338517494</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1099337473332938</v>
+        <v>-0.1276587041659672</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.02458250494518266</v>
+        <v>0.2056334096237578</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.0290971967494188</v>
+        <v>-0.02453410338318848</v>
       </c>
       <c r="CI7" t="n">
         <v>0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
@@ -4117,19 +4117,19 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.004781864178744051</v>
+        <v>-0.07979726036256821</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.1652687644090485</v>
+        <v>0.4767099570284105</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.1535734289989721</v>
+        <v>0.233459604695158</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,28 +4138,28 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.1016666405037144</v>
+        <v>-0.129497199147023</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.05748812621578336</v>
+        <v>0.2122364072197847</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.01887670091101827</v>
+        <v>-0.006090763733027389</v>
       </c>
       <c r="DA7" t="n">
         <v>-0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
@@ -4171,46 +4171,46 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.1435265951183348</v>
+        <v>-0.2273386839039436</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.005301379174500657</v>
+        <v>0.08969896046372131</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.02185486618278355</v>
+        <v>-0.1083099664785625</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.01930335594717677</v>
+        <v>-0.03167446273453241</v>
       </c>
       <c r="DP7" t="n">
         <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.1034395124751792</v>
+        <v>0.0449575454442345</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.06937717261553171</v>
+        <v>0.04101016695594945</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
@@ -4222,79 +4222,79 @@
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0538120128486075</v>
+        <v>-0.02978470338873303</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.01149759408282369</v>
+        <v>-0.1320741472473067</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.02139786954275834</v>
+        <v>-0.1369395725517401</v>
       </c>
       <c r="EB7" t="n">
         <v>0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1072186284226279</v>
+        <v>-0.07209744881768181</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.0380931759527465</v>
+        <v>0.175999303720743</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.080526113057247</v>
+        <v>0.0161262420560592</v>
       </c>
       <c r="EK7" t="n">
         <v>0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.1041666885838893</v>
+        <v>-0.1581303005255985</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.07462981083725337</v>
+        <v>0.1230363003184724</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.00290782575919066</v>
+        <v>0.003750531403896452</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4303,25 +4303,25 @@
         <v>-0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.1024802412484532</v>
+        <v>-0.1585258595002308</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.03431644791390573</v>
+        <v>0.238355241246916</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.02945956859646489</v>
+        <v>-0.02327057194261592</v>
       </c>
       <c r="FC7" t="n">
         <v>0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
@@ -4330,19 +4330,19 @@
         <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.001873037695619126</v>
+        <v>-0.1363025392287527</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.0868378773614245</v>
+        <v>0.1698390885284941</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.003597478908403023</v>
+        <v>0.07123925082052153</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
@@ -4351,61 +4351,61 @@
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
         <v>0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.005241059149449562</v>
+        <v>-0.02654794237536354</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.03723094875847665</v>
+        <v>0.0379584166868465</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.001880625472475258</v>
+        <v>0.03564666313591682</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.01112504221783289</v>
+        <v>-0.2171248100715393</v>
       </c>
       <c r="GA7" t="n">
         <v>-0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.09361181504413613</v>
+        <v>0.1375972415649666</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
         <v>-0</v>
@@ -4416,19 +4416,19 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1672268754992563</v>
+        <v>0.4971129380280747</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.009364916934062353</v>
+        <v>-0.03121206849111895</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1037538337376321</v>
+        <v>-0.1564159387552574</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -4443,76 +4443,76 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1621356121045718</v>
+        <v>0.8230477561609622</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.003513511902966232</v>
+        <v>-0.1563533855105173</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1678180381712661</v>
+        <v>-0.2291705864469435</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02135519773272989</v>
+        <v>0.266271668164037</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.03653675314498834</v>
+        <v>-0.1226164678287812</v>
       </c>
       <c r="X8" t="n">
-        <v>0.006236065107407949</v>
+        <v>-0.04320652051487218</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.03096819916375399</v>
+        <v>0.08912711352921013</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.03549222191081662</v>
+        <v>-0.4604797709814444</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.003988903703998697</v>
+        <v>-0.203747479963447</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
@@ -4521,22 +4521,22 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01147613571919206</v>
+        <v>0.2791774529855735</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.02355846438024706</v>
+        <v>0.1197107078137764</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.04688198737750695</v>
+        <v>-0.1106035062240687</v>
       </c>
       <c r="AQ8" t="n">
         <v>-0</v>
@@ -4548,10 +4548,10 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.1474648013925624</v>
+        <v>1.028561682259372</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
@@ -4560,16 +4560,16 @@
         <v>-0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.02987885309985442</v>
+        <v>-0.1531530147526411</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.102495837626316</v>
+        <v>-0.3762408293921216</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
         <v>0</v>
@@ -4578,76 +4578,76 @@
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.04355603959234695</v>
+        <v>-0.0709090138538665</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.01128088934417675</v>
+        <v>-0.1240301476805323</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.01779459368573299</v>
+        <v>-0.02701284865698827</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
         <v>0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0621341498770692</v>
+        <v>0.03351717041990425</v>
       </c>
       <c r="BN8" t="n">
         <v>0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.01922593914948021</v>
+        <v>0.1448707271485718</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.02425514638463136</v>
+        <v>-0.07567227388962566</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.07719429697720605</v>
+        <v>0.7037045611785685</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.004334159979247251</v>
+        <v>-0.06347234111202348</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.03493862441281084</v>
+        <v>-0.2198636297552389</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB8" t="n">
         <v>-0</v>
@@ -4659,61 +4659,61 @@
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.04566578077951314</v>
+        <v>-0.2939580635598096</v>
       </c>
       <c r="CF8" t="n">
         <v>0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.006160915539447832</v>
+        <v>0.05914150581219765</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.04172555807445631</v>
+        <v>0.1403744975661385</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.01705254750254112</v>
+        <v>-0.6345955767832731</v>
       </c>
       <c r="CO8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.006074231258450518</v>
+        <v>0.3690821831765571</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.03215439113313784</v>
+        <v>0.3089599766253668</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
         <v>-0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.03580442554339727</v>
+        <v>-0.2775910825426457</v>
       </c>
       <c r="CX8" t="n">
         <v>-0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.008846326920091289</v>
+        <v>0.02033574017213782</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.04374248514174967</v>
+        <v>0.1209019756202149</v>
       </c>
       <c r="DB8" t="n">
         <v>0</v>
@@ -4740,52 +4740,52 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.04723440316909285</v>
+        <v>-0.08602887854061321</v>
       </c>
       <c r="DG8" t="n">
         <v>-0</v>
       </c>
       <c r="DH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.04733929678032048</v>
+        <v>-0.3469391125817477</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.002874834700390242</v>
+        <v>-0.0001575358778293421</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
       </c>
       <c r="DL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.02811082095000961</v>
+        <v>-0.1727185100760718</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0193049504296051</v>
+        <v>0.1045826101202992</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.006713248489600037</v>
+        <v>-0.008345674942087251</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.02461495946005643</v>
+        <v>0.05975287600916222</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
@@ -4803,10 +4803,10 @@
         <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.01487447220214145</v>
+        <v>0.09486500237337603</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.02508276763326615</v>
+        <v>-0.2009803230799578</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
@@ -4815,40 +4815,40 @@
         <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
         <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.03380968900669276</v>
+        <v>-0.03955144918738402</v>
       </c>
       <c r="EH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
         <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.006321095356972036</v>
+        <v>-0.09440431138490248</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.02091731584528292</v>
+        <v>0.02564454393629453</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
         <v>-0</v>
       </c>
       <c r="EN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.01515496316239557</v>
+        <v>-0.07198483638857861</v>
       </c>
       <c r="EQ8" t="n">
         <v>0</v>
@@ -4857,10 +4857,10 @@
         <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.01465789132401625</v>
+        <v>-0.1219731208720478</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.03752582229647378</v>
+        <v>0.02438716733961008</v>
       </c>
       <c r="EU8" t="n">
         <v>-0</v>
@@ -4875,22 +4875,22 @@
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.03655258232067119</v>
+        <v>-0.3094055936986613</v>
       </c>
       <c r="EZ8" t="n">
         <v>0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.003107910883587261</v>
+        <v>0.005754119277899252</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.04623045616462187</v>
+        <v>0.1089857822531026</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
@@ -4902,7 +4902,7 @@
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.002754138407305414</v>
+        <v>-0.3446950761586405</v>
       </c>
       <c r="FI8" t="n">
         <v>-0</v>
@@ -4911,37 +4911,37 @@
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.02984668508877564</v>
+        <v>0.1886379381846389</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.03070874923635799</v>
+        <v>0.1005440412989026</v>
       </c>
       <c r="FM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.002503515516889058</v>
+        <v>-0.0667401501268387</v>
       </c>
       <c r="FR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.0009692457530458859</v>
+        <v>0.01899367764615194</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.02561620727964271</v>
+        <v>0.1120919509804363</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
@@ -4950,13 +4950,13 @@
         <v>-0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.01469792746268163</v>
+        <v>-0.1490284180992962</v>
       </c>
       <c r="GA8" t="n">
         <v>-0</v>
@@ -4968,13 +4968,13 @@
         <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.03675813158824143</v>
+        <v>-0.03629910302019451</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
         <v>0</v>
@@ -5551,19 +5551,19 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4140870251896734</v>
+        <v>0.01015747529634157</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1819719553223891</v>
+        <v>-0.00428353183756343</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5572,25 +5572,25 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3490912522651025</v>
+        <v>-0.003328903821150875</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.355989419828883</v>
+        <v>0.01697565987270643</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3508948132114816</v>
+        <v>-0.01111092711889036</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5599,34 +5599,34 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.6824205591970134</v>
+        <v>-0.009963479839822468</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2997504238426291</v>
+        <v>0.00795469004446488</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3016994831758418</v>
+        <v>-0.007613583690055601</v>
       </c>
       <c r="X10" t="n">
         <v>-0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.07871805453071325</v>
+        <v>-0.003615094971350008</v>
       </c>
       <c r="AA10" t="n">
         <v>-0</v>
@@ -5635,16 +5635,16 @@
         <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.277263828410642</v>
+        <v>-0.00659102492223917</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.1285582305635437</v>
+        <v>-0.009993828749528781</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -5653,34 +5653,34 @@
         <v>-0</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.256823877133243</v>
+        <v>0.002866032762689753</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.1052747926201442</v>
+        <v>0.00593667121990048</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.01225457983934452</v>
+        <v>0.000768252595833724</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.1796001090889973</v>
+        <v>-0.0002534225520035782</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,7 +5689,7 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.8347455729376775</v>
+        <v>0.0193168180421625</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
@@ -5698,43 +5698,43 @@
         <v>-0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.4188888631987313</v>
+        <v>-0.001562141597405093</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ10" t="n">
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0.005225754675405844</v>
+        <v>-0.004205128224301895</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.01236277987786707</v>
+        <v>-0.004074687796260064</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.2221493227095833</v>
+        <v>-0.007129536804819541</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI10" t="n">
         <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-0.1343274306746161</v>
+        <v>-0.0003096064778019369</v>
       </c>
       <c r="BK10" t="n">
         <v>-0</v>
@@ -5743,7 +5743,7 @@
         <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.4005807370879286</v>
+        <v>0.005432245929346308</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
@@ -5752,16 +5752,16 @@
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.6455695079607542</v>
+        <v>0.01046637478720863</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.2605468571871966</v>
+        <v>0.005147452941403772</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
@@ -5770,43 +5770,43 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.4027506831898156</v>
+        <v>0.01685930611955803</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.2082612957935103</v>
+        <v>-0.001848601506627989</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.04801709783643932</v>
+        <v>-0.007037826872812624</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.1581870589945097</v>
+        <v>-0.002751136787714545</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.02763196294649435</v>
+        <v>0.002235991160757094</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
@@ -5815,16 +5815,16 @@
         <v>-0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.1636103870407351</v>
+        <v>0.00232667867040571</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.3768478778391208</v>
+        <v>-0.004504168594770574</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
@@ -5833,34 +5833,34 @@
         <v>0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.4807812920364518</v>
+        <v>0.008767921627548131</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0.1534521215108039</v>
+        <v>0.003143187385796403</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.1252608511230929</v>
+        <v>-0.002681341500816842</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.03425326332804163</v>
+        <v>0.00217881102380715</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5869,52 +5869,52 @@
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.07486703056198475</v>
+        <v>0.003593220597619712</v>
       </c>
       <c r="DD10" t="n">
         <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.6270653622812298</v>
+        <v>-0.003235257981242775</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.1399931986169113</v>
+        <v>0.002159784116394602</v>
       </c>
       <c r="DJ10" t="n">
         <v>0</v>
       </c>
       <c r="DK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0.04106261950825694</v>
+        <v>0.000870986650077618</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.1610958865037532</v>
+        <v>-0.004634842977229247</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.0961220953795644</v>
+        <v>-0.001714701315102501</v>
       </c>
       <c r="DS10" t="n">
         <v>-0</v>
@@ -5923,16 +5923,16 @@
         <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.1232720427854635</v>
+        <v>0.0005097325500827474</v>
       </c>
       <c r="DV10" t="n">
         <v>-0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.07316721113832779</v>
+        <v>0.004134904658079512</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
@@ -5941,34 +5941,34 @@
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.05557996483449301</v>
+        <v>-0.004867117589893731</v>
       </c>
       <c r="EB10" t="n">
         <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0.1536339370952199</v>
+        <v>-0.007075947595516378</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.08115578207185493</v>
+        <v>0.003414576135702802</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.06517392569115647</v>
+        <v>-0.001337092396166099</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,16 +5977,16 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.1815468619850599</v>
+        <v>-0.0008396223948571184</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.05501183340937445</v>
+        <v>-0.001144314553957243</v>
       </c>
       <c r="EQ10" t="n">
         <v>0</v>
@@ -5995,34 +5995,34 @@
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.1125568309675179</v>
+        <v>-0.003012661759234157</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
         <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.01309333194210422</v>
+        <v>0.003224337684656244</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.1109524871834533</v>
+        <v>-0.002799434702788986</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.04377370597562613</v>
+        <v>0.0002735181281901148</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
@@ -6031,43 +6031,43 @@
         <v>-0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.150456350033064</v>
+        <v>0.003449696159991477</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.05787094940502054</v>
+        <v>0.000570431601505457</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.1079717948810323</v>
+        <v>0.00571385779667958</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0.1020069453364108</v>
+        <v>-0.002557980564260726</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0198619356171281</v>
+        <v>-0.0003850792413193293</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
@@ -6076,96 +6076,96 @@
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.04373087886308043</v>
+        <v>0.001270062395504973</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0.1717979940822003</v>
+        <v>0.0008087229184138031</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.3103215357345082</v>
+        <v>-0.00546434319203833</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
         <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
         <v>0</v>
       </c>
       <c r="GE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF10" t="n">
-        <v>-0.3110226453760752</v>
+        <v>-0.001578005207898021</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.2368517741760804</v>
+        <v>-0.2163281285375999</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4282401006139772</v>
+        <v>0.2725489642219895</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1573692507205403</v>
+        <v>-0.08593243318096838</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.174760971132089</v>
+        <v>-0.1331094492976495</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3774262678156114</v>
+        <v>0.4301226302612453</v>
       </c>
       <c r="L11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3689118832412238</v>
+        <v>-0.1109522891329522</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -6174,19 +6174,19 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0198286142443377</v>
+        <v>0.05798243167400864</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2974699869538441</v>
+        <v>0.08714645519770231</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2045045208196993</v>
+        <v>0.02470721830643885</v>
       </c>
       <c r="X11" t="n">
         <v>-0</v>
@@ -6195,106 +6195,106 @@
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.04029494930087998</v>
+        <v>-0.1197811264864801</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1747387454736785</v>
+        <v>-0.1013629233703756</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.06874581500373328</v>
+        <v>-0.1530427158837961</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.09689097591192863</v>
+        <v>-0.005073422530013782</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.1952485393767772</v>
+        <v>0.183088564764974</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.03204929432310592</v>
+        <v>-0.06212754514026096</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.19625669046297</v>
+        <v>0.01748677425511655</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.5714201424047074</v>
+        <v>0.3696574730614147</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.3243467649744163</v>
+        <v>-0.123889190409415</v>
       </c>
       <c r="AY11" t="n">
         <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
         <v>-0</v>
       </c>
       <c r="BC11" t="n">
-        <v>-0.1358599968127568</v>
+        <v>-0.1798034413081816</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.04735088819037612</v>
+        <v>-0.02060157450573912</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.2823883685094337</v>
+        <v>-0.1053262688214306</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
@@ -6309,10 +6309,10 @@
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0.08196304950153938</v>
+        <v>0.04766672648315647</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.07509965987434392</v>
+        <v>0.1854459633750977</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
@@ -6321,13 +6321,13 @@
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.2918258830562541</v>
+        <v>0.09545733484052796</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
@@ -6336,49 +6336,49 @@
         <v>-0</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.106860543647104</v>
+        <v>0.09011171331143703</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.3525163971840918</v>
+        <v>0.3890593309699328</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.08165572047983688</v>
+        <v>-0.01667883359831406</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
         <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.03912409604200023</v>
+        <v>0.0747494156950993</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.1044872426587082</v>
+        <v>-0.1312030424085893</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.01364911348721125</v>
+        <v>0.01798170005886309</v>
       </c>
       <c r="CI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ11" t="n">
         <v>-0</v>
@@ -6390,46 +6390,46 @@
         <v>-0</v>
       </c>
       <c r="CM11" t="n">
-        <v>-0.264636593056403</v>
+        <v>-0.07976563659569219</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.1110022112502398</v>
+        <v>-0.2866405686346317</v>
       </c>
       <c r="CO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP11" t="n">
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.2842175674428912</v>
+        <v>0.09781581620856597</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
         <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.01873097448300696</v>
+        <v>0.04748236190567322</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.1179411800838</v>
+        <v>-0.1281611215548974</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.006335041887522175</v>
+        <v>-0.007268842713396832</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
@@ -6444,37 +6444,37 @@
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.2480050885538153</v>
+        <v>0.02860112652130634</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.398951217553391</v>
+        <v>-0.2791701251701793</v>
       </c>
       <c r="DG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH11" t="n">
         <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.06623550118849042</v>
+        <v>-0.001669662161821843</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL11" t="n">
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0.1325273493652447</v>
+        <v>-0.02762757930611718</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.1692864223476128</v>
+        <v>-0.04826322991158558</v>
       </c>
       <c r="DP11" t="n">
         <v>-0</v>
@@ -6483,61 +6483,61 @@
         <v>-0</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.05275197622694023</v>
+        <v>0.02116532359099054</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
-        <v>-0.04332125458465274</v>
+        <v>0.1384077748328482</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.1323553265061046</v>
+        <v>0.1623016394342358</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.1039013379236078</v>
+        <v>-0.07089503300746447</v>
       </c>
       <c r="EB11" t="n">
         <v>0</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>-0.05903344221007327</v>
+        <v>-0.006814690987866357</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.1580531756825727</v>
+        <v>0.006064018702745473</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
         <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.004426425765733766</v>
+        <v>-0.04300964376514718</v>
       </c>
       <c r="EK11" t="n">
         <v>-0</v>
@@ -6552,19 +6552,19 @@
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>-0.03224915333081991</v>
+        <v>-0.02377235109815298</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.09697559498066002</v>
+        <v>-0.09105368605779271</v>
       </c>
       <c r="EQ11" t="n">
         <v>0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.02938001701136138</v>
+        <v>-0.09828727179900379</v>
       </c>
       <c r="ET11" t="n">
         <v>-0</v>
@@ -6573,16 +6573,16 @@
         <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
         <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.03723101467982912</v>
+        <v>0.05964594162611744</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.1101899691962202</v>
+        <v>-0.1639899903141915</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
@@ -6591,79 +6591,79 @@
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.05234479266363937</v>
+        <v>-0.02174312973877673</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>-0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.1604652513162104</v>
+        <v>0.009342622972610747</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.05408729984846706</v>
+        <v>-0.01332187891622046</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.08636732447195747</v>
+        <v>0.009959407848905054</v>
       </c>
       <c r="FL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>-0.009796257125295462</v>
+        <v>-0.01744169827038777</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.02981959444214748</v>
+        <v>0.01188518190020146</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.01399334328176596</v>
+        <v>0.05693162042055831</v>
       </c>
       <c r="FU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
         <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0.06397056932381519</v>
+        <v>0.05418765583236028</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.154638663704746</v>
+        <v>-0.1055292918857475</v>
       </c>
       <c r="GA11" t="n">
         <v>-0</v>
@@ -6672,10 +6672,10 @@
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6684,7 +6684,7 @@
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,34 +6692,34 @@
         <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5319002917270482</v>
+        <v>0.02915963600945904</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2661096760720325</v>
+        <v>-0.06786519059753461</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2754485098676538</v>
+        <v>-0.0748135851448237</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3914847244747058</v>
+        <v>0.06882424113470297</v>
       </c>
       <c r="L12" t="n">
         <v>-0</v>
@@ -6728,13 +6728,13 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2865320058554609</v>
+        <v>-0.06826362172458814</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2411154436742089</v>
+        <v>-0.1090338149610001</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -6746,22 +6746,22 @@
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2001135802293743</v>
+        <v>0.03427271420808858</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
         <v>-0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2163492355642851</v>
+        <v>-0.02480515272084749</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.03278122765144969</v>
+        <v>0.02968573728701496</v>
       </c>
       <c r="Z12" t="n">
         <v>-0</v>
@@ -6773,52 +6773,52 @@
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.2336979224752768</v>
+        <v>-0.07020263926977134</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>-0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.05971446741888643</v>
+        <v>-0.1179178888661541</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.02885837113151845</v>
+        <v>0.01789223895188168</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.07116912773160655</v>
+        <v>0.08437342289745738</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.002361533144790778</v>
+        <v>0.01519202519808491</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.07685322296462661</v>
+        <v>0.01570920115915254</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
@@ -6827,7 +6827,7 @@
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.6047274890572939</v>
+        <v>0.181182211679755</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
@@ -6836,40 +6836,40 @@
         <v>-0</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.0115537155990397</v>
+        <v>0.01475851584004415</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.1791874886932588</v>
+        <v>0.001622697909947252</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
         <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.1034041116129616</v>
+        <v>-0.08785358514629837</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF12" t="n">
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1038779505801347</v>
+        <v>-0.08012724555023459</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0.1130061446088581</v>
+        <v>-0.02553170173517899</v>
       </c>
       <c r="BJ12" t="n">
         <v>0</v>
@@ -6878,10 +6878,10 @@
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0989788042203491</v>
+        <v>-0.01201817681488031</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
@@ -6890,13 +6890,13 @@
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.2144506903881195</v>
+        <v>0.05425783309765145</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.01320690767790568</v>
+        <v>0.05243627002747486</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,34 +6908,34 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2568923576534772</v>
+        <v>0.1345948441133588</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.01101386406577786</v>
+        <v>-0.01162798422390383</v>
       </c>
       <c r="BZ12" t="n">
         <v>-0</v>
       </c>
       <c r="CA12" t="n">
-        <v>-0.07900306065349984</v>
+        <v>-0.0001841882160224279</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1492530107271576</v>
+        <v>-0.01047325266291159</v>
       </c>
       <c r="CF12" t="n">
         <v>0</v>
@@ -6944,13 +6944,13 @@
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.0561261269205712</v>
+        <v>0.02523279188134427</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.07014439578496735</v>
+        <v>0.01258630302813271</v>
       </c>
       <c r="CK12" t="n">
         <v>-0</v>
@@ -6959,25 +6959,25 @@
         <v>-0</v>
       </c>
       <c r="CM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.2226758527595059</v>
+        <v>-0.06073587283230945</v>
       </c>
       <c r="CO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP12" t="n">
         <v>0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.1742500616519252</v>
+        <v>0.04314498959390645</v>
       </c>
       <c r="CR12" t="n">
         <v>0</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0.002958869899430355</v>
+        <v>-0.07579226859969702</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
@@ -6986,10 +6986,10 @@
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.1174994978917539</v>
+        <v>-0.01339758105006465</v>
       </c>
       <c r="CX12" t="n">
         <v>-0</v>
@@ -6998,13 +6998,13 @@
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.04738991420473637</v>
+        <v>0.02534634082149168</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.05932863350967378</v>
+        <v>0.02051879013296967</v>
       </c>
       <c r="DC12" t="n">
         <v>0</v>
@@ -7013,106 +7013,106 @@
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.3632276956030513</v>
+        <v>-0.02631895694238418</v>
       </c>
       <c r="DG12" t="n">
         <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.05058938401573208</v>
+        <v>-0.004066639270895562</v>
       </c>
       <c r="DJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0.09472961123975748</v>
+        <v>-0.03358409771336528</v>
       </c>
       <c r="DL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM12" t="n">
         <v>-0</v>
       </c>
       <c r="DN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.08283639822856918</v>
+        <v>0.003275177171399707</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.03548680634423883</v>
+        <v>0.05626961004718882</v>
       </c>
       <c r="DS12" t="n">
         <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>-0.02693962062150807</v>
+        <v>0.03769224477632082</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.147683079975484</v>
+        <v>0.01062651550965603</v>
       </c>
       <c r="DY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ12" t="n">
         <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.07727394207194675</v>
+        <v>-0.03617092165367131</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.003573631958904973</v>
+        <v>0.001465343193732573</v>
       </c>
       <c r="ED12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.0393977209996528</v>
+        <v>-0.01297512341134143</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.08787749250488164</v>
+        <v>0.00806019035054239</v>
       </c>
       <c r="EK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.08425858481205242</v>
+        <v>-0.01615905547402571</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
@@ -7121,10 +7121,10 @@
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.04861989198257095</v>
+        <v>-0.001680669138317035</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
@@ -7133,25 +7133,25 @@
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.04855422744376831</v>
+        <v>-0.007559182545449411</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.01603423170886747</v>
+        <v>-0.02751321109679665</v>
       </c>
       <c r="EV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW12" t="n">
         <v>0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.1286370965407103</v>
+        <v>-0.009405538733801665</v>
       </c>
       <c r="EZ12" t="n">
         <v>0</v>
@@ -7160,13 +7160,13 @@
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.04754719662577281</v>
+        <v>0.01391173508666804</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.05890110439714463</v>
+        <v>0.01010816647832563</v>
       </c>
       <c r="FE12" t="n">
         <v>-0</v>
@@ -7175,25 +7175,25 @@
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.0421094352705843</v>
+        <v>-0.02411621663999343</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.113959104034843</v>
+        <v>-0.02355979453028976</v>
       </c>
       <c r="FL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.06419630585364511</v>
+        <v>-0.0145095986979792</v>
       </c>
       <c r="FN12" t="n">
         <v>-0</v>
@@ -7205,7 +7205,7 @@
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.01024425265711541</v>
+        <v>-0.01339646422062393</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
@@ -7214,28 +7214,28 @@
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.01131290628212045</v>
+        <v>-0.006257607245206566</v>
       </c>
       <c r="FU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.05368233383618497</v>
+        <v>0.05350396626919097</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
         <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.1114233156106896</v>
+        <v>-0.0457954831019726</v>
       </c>
       <c r="GA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB12" t="n">
         <v>-0</v>
@@ -7244,16 +7244,16 @@
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>-0.00698406245480016</v>
+        <v>0.02698442369642013</v>
       </c>
       <c r="GF12" t="n">
         <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7675229500376433</v>
+        <v>1.254886355468094</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2393504694053548</v>
+        <v>-0.7257672611372614</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -7282,13 +7282,13 @@
         <v>-0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4232904237368065</v>
+        <v>-0.2513054839494331</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5502701248450331</v>
+        <v>1.699457250414853</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,25 +7297,25 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3122885906228083</v>
+        <v>-0.8348191627246587</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.431468246609088</v>
+        <v>-0.2607357859083715</v>
       </c>
       <c r="S13" t="n">
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.270059812103028</v>
+        <v>0.2937602118455535</v>
       </c>
       <c r="U13" t="n">
         <v>-0</v>
@@ -7324,88 +7324,88 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.04510855597724524</v>
+        <v>-0.2478042941953067</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z13" t="n">
         <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.08745374345584193</v>
+        <v>-0.2615464269133965</v>
       </c>
       <c r="AB13" t="n">
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.3183565104320905</v>
+        <v>0.197504567421979</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.0581203195657155</v>
+        <v>-0.4346492454941048</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.008073733655733783</v>
+        <v>0.005867761325806635</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.1492042834533128</v>
+        <v>0.6894899261730145</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.01175105596037616</v>
+        <v>0.3307997334691035</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0.03137396414934696</v>
+        <v>-0.01189735114385449</v>
       </c>
       <c r="AT13" t="n">
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.7848121894060394</v>
+        <v>2.013351183237102</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.1140060567599054</v>
+        <v>-0.3078403626209361</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -7417,13 +7417,13 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0.2494948482116723</v>
+        <v>0.04096540733796719</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.0811016873824433</v>
+        <v>-0.3642178929982842</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,7 +7432,7 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.2184532147657136</v>
+        <v>-0.4906793882796077</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
@@ -7441,16 +7441,16 @@
         <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0.1767811405067999</v>
+        <v>-0.09350075979408383</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0546120120886987</v>
+        <v>0.1443626502565902</v>
       </c>
       <c r="BN13" t="n">
         <v>-0</v>
@@ -7459,52 +7459,52 @@
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.3381071370694067</v>
+        <v>0.3364634382650667</v>
       </c>
       <c r="BQ13" t="n">
         <v>-0</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.006649564079545768</v>
+        <v>0.2082959141878342</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.4648441843800752</v>
+        <v>1.290886179768173</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.06069589861683189</v>
+        <v>-0.3178128370281049</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0.1014008557503341</v>
+        <v>-0.2485952225225648</v>
       </c>
       <c r="CD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.189542135070138</v>
+        <v>-0.6453516075938712</v>
       </c>
       <c r="CF13" t="n">
         <v>-0</v>
@@ -7513,34 +7513,34 @@
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.02451081645098459</v>
+        <v>0.166934655274397</v>
       </c>
       <c r="CI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.1482036050265327</v>
+        <v>0.09987510768502243</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.2260435167011973</v>
+        <v>-1.207796518931482</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
         <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.2245544265899017</v>
+        <v>0.2375954820029037</v>
       </c>
       <c r="CR13" t="n">
         <v>0</v>
@@ -7552,40 +7552,40 @@
         <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.05786722142276653</v>
+        <v>-0.00582245176515982</v>
       </c>
       <c r="CV13" t="n">
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.1613641109128821</v>
+        <v>-0.6039905357558182</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.03500069348632016</v>
+        <v>0.1188173574365486</v>
       </c>
       <c r="DA13" t="n">
         <v>0</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.1075833058884473</v>
+        <v>0.1432244670744477</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.450607184291181</v>
+        <v>-0.3538181358716258</v>
       </c>
       <c r="DG13" t="n">
         <v>-0</v>
@@ -7594,7 +7594,7 @@
         <v>-0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.1084714720882998</v>
+        <v>-0.02527396891207903</v>
       </c>
       <c r="DJ13" t="n">
         <v>-0</v>
@@ -7606,22 +7606,22 @@
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.01832638307279654</v>
+        <v>-0.1404687227536884</v>
       </c>
       <c r="DN13" t="n">
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.08361745939022677</v>
+        <v>-0.299883734449631</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.0003985997279781389</v>
+        <v>0.09435456649110265</v>
       </c>
       <c r="DS13" t="n">
         <v>-0</v>
@@ -7630,16 +7630,16 @@
         <v>0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0.03801975161875711</v>
+        <v>-0.279007306763618</v>
       </c>
       <c r="DW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.1713429556039515</v>
+        <v>0.5042941016542896</v>
       </c>
       <c r="DY13" t="n">
         <v>-0</v>
@@ -7648,64 +7648,64 @@
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.06260383389727746</v>
+        <v>-0.1737558746458866</v>
       </c>
       <c r="EB13" t="n">
         <v>-0</v>
       </c>
       <c r="EC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>-0.002041737485253598</v>
+        <v>0.3317438909602231</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.01183480307789825</v>
+        <v>-0.2549207437911949</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.05333373573440357</v>
+        <v>-0.03365267002132949</v>
       </c>
       <c r="EK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.2080372336071113</v>
+        <v>0.06199355205441569</v>
       </c>
       <c r="EO13" t="n">
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.1257137851085801</v>
+        <v>-0.373131056669463</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.006573926987699884</v>
+        <v>0.08825955149261835</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU13" t="n">
         <v>0</v>
@@ -7714,13 +7714,13 @@
         <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.01889365856432744</v>
+        <v>0.1436034619245373</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.1900229989856457</v>
+        <v>-0.7201912355856707</v>
       </c>
       <c r="EZ13" t="n">
         <v>-0</v>
@@ -7729,100 +7729,100 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.01417379748764352</v>
+        <v>0.1108088006337201</v>
       </c>
       <c r="FC13" t="n">
         <v>-0</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.09924223091910823</v>
+        <v>0.152392457200056</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.09264559624657331</v>
+        <v>-0.2322300172029111</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.06220429217900583</v>
+        <v>-0.05783612905501098</v>
       </c>
       <c r="FL13" t="n">
         <v>0</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>-0.1378059685564795</v>
+        <v>-0.1800278315482582</v>
       </c>
       <c r="FP13" t="n">
         <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.01578362117967838</v>
+        <v>-0.04567674968173364</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.006221354128122514</v>
+        <v>0.07438107798260715</v>
       </c>
       <c r="FU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.03474151670704284</v>
+        <v>-0.1051670551044763</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.2112114121332656</v>
+        <v>-0.3332908540460921</v>
       </c>
       <c r="GA13" t="n">
         <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC13" t="n">
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0.03826524230169872</v>
+        <v>0.1249423121749635</v>
       </c>
     </row>
     <row r="14">
@@ -8396,28 +8396,28 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.2423175276693852</v>
+        <v>0.495593410469774</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.07052425005005317</v>
+        <v>-0.08520363215062633</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.09114837792202443</v>
+        <v>-0.3914635716977827</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G15" t="n">
         <v>-0</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -8426,25 +8426,25 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1936105335099626</v>
+        <v>0.7735323124108373</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.04596381085413895</v>
+        <v>-0.06185121805317301</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1333756895739681</v>
+        <v>-0.3986221831348117</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P15" t="n">
         <v>-0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -8453,46 +8453,46 @@
         <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.06176957451717052</v>
+        <v>0.1674574937169372</v>
       </c>
       <c r="U15" t="n">
-        <v>0.002036085664480468</v>
+        <v>0.09288735014444169</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.01110247495286459</v>
+        <v>0.1285600970173655</v>
       </c>
       <c r="X15" t="n">
         <v>-0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.07904564193266715</v>
+        <v>-0.03362043593175831</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.007084872520625183</v>
+        <v>-0.2536771461472846</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.02317513223021877</v>
+        <v>-0.1568835491655169</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH15" t="n">
         <v>-0</v>
@@ -8504,46 +8504,46 @@
         <v>-0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.06793144158849806</v>
+        <v>0.3280145483650992</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0.003787130187296552</v>
+        <v>0.03265046916486685</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.01669958603091842</v>
+        <v>0.2073223313676478</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT15" t="n">
         <v>-0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.1954572017155776</v>
+        <v>0.7393077570917517</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.0455409207563201</v>
+        <v>0.2300330729306871</v>
       </c>
       <c r="AW15" t="n">
         <v>-0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.02117715627409004</v>
+        <v>-0.003863383422877335</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
@@ -8552,34 +8552,34 @@
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.05018916842587316</v>
+        <v>-0.275935955770882</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.0331346605761492</v>
+        <v>-0.1968686950977141</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.09365940520716383</v>
+        <v>-0.4381550095219632</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI15" t="n">
         <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
@@ -8588,25 +8588,25 @@
         <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.03480585396374154</v>
+        <v>0.04568666941767389</v>
       </c>
       <c r="BN15" t="n">
-        <v>-0.02038261114742641</v>
+        <v>-0.04169077800239546</v>
       </c>
       <c r="BO15" t="n">
         <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.03620651822235817</v>
+        <v>0.1284456632242259</v>
       </c>
       <c r="BQ15" t="n">
         <v>-0</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT15" t="n">
         <v>-0</v>
@@ -8615,52 +8615,52 @@
         <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.110107887266753</v>
+        <v>0.6071742141990265</v>
       </c>
       <c r="BW15" t="n">
-        <v>-0.05205167447252523</v>
+        <v>0.1062373845424915</v>
       </c>
       <c r="BX15" t="n">
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.007350922972350669</v>
+        <v>0.03441418421346509</v>
       </c>
       <c r="BZ15" t="n">
         <v>-0</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.04670862580849976</v>
+        <v>-0.2760816243084407</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.005407675475689114</v>
+        <v>0.03776511378406863</v>
       </c>
       <c r="CG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.01912298140153196</v>
+        <v>0.1031446191051352</v>
       </c>
       <c r="CI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL15" t="n">
         <v>-0</v>
@@ -8669,16 +8669,16 @@
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.02465172274197945</v>
+        <v>-0.466543568527515</v>
       </c>
       <c r="CO15" t="n">
-        <v>-0.0139938825383469</v>
+        <v>0.01828523897445258</v>
       </c>
       <c r="CP15" t="n">
         <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.01746131664655941</v>
+        <v>0.1495340930255932</v>
       </c>
       <c r="CR15" t="n">
         <v>0</v>
@@ -8693,19 +8693,19 @@
         <v>0</v>
       </c>
       <c r="CV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.03434450806259039</v>
+        <v>-0.2528473880386228</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0.001680062560800156</v>
+        <v>0.04077296214095102</v>
       </c>
       <c r="CY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.009208919355260383</v>
+        <v>0.05857936639919568</v>
       </c>
       <c r="DA15" t="n">
         <v>0</v>
@@ -8720,19 +8720,19 @@
         <v>0</v>
       </c>
       <c r="DE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.0404637587788606</v>
+        <v>-0.1963852487799621</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.01276274861884548</v>
+        <v>-0.0112748599245017</v>
       </c>
       <c r="DH15" t="n">
         <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.01243582658283967</v>
+        <v>0.02145360129637881</v>
       </c>
       <c r="DJ15" t="n">
         <v>-0</v>
@@ -8750,19 +8750,19 @@
         <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.02300074156306127</v>
+        <v>-0.1274925339322433</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.006951652254949176</v>
+        <v>-0.08974145424494288</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.008683192370150262</v>
+        <v>0.1591028612338508</v>
       </c>
       <c r="DS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT15" t="n">
         <v>0</v>
@@ -8771,130 +8771,130 @@
         <v>-0</v>
       </c>
       <c r="DV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.01587226096435545</v>
+        <v>0.3578387978206652</v>
       </c>
       <c r="DY15" t="n">
-        <v>-0.01455002698464741</v>
+        <v>0.05235592229558594</v>
       </c>
       <c r="DZ15" t="n">
         <v>0</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.007720299928725771</v>
+        <v>-0.2162633606323541</v>
       </c>
       <c r="EB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
         <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.01234302050060933</v>
+        <v>-0.09349501475274485</v>
       </c>
       <c r="EH15" t="n">
-        <v>-0.002703665588768782</v>
+        <v>-0.04247261417857989</v>
       </c>
       <c r="EI15" t="n">
         <v>0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.04063398539425512</v>
+        <v>0.02554614680432664</v>
       </c>
       <c r="EK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN15" t="n">
         <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.01309390247951039</v>
+        <v>-0.1767034298348411</v>
       </c>
       <c r="EQ15" t="n">
-        <v>-0.03756222455788923</v>
+        <v>-0.07378290908131005</v>
       </c>
       <c r="ER15" t="n">
         <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.03310334595544871</v>
+        <v>-0.02432384579677651</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU15" t="n">
         <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.04156851571289946</v>
+        <v>-0.2882457192471997</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.00195878923855244</v>
+        <v>0.02741347663599262</v>
       </c>
       <c r="FA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.02009801110362146</v>
+        <v>0.06261243505002842</v>
       </c>
       <c r="FC15" t="n">
         <v>-0</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF15" t="n">
         <v>-0</v>
       </c>
       <c r="FG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.03754034272753051</v>
+        <v>0.06013243159152277</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0.0235482357775186</v>
+        <v>-0.2255253683839344</v>
       </c>
       <c r="FJ15" t="n">
         <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.05436451404540103</v>
+        <v>-0.1867296848828588</v>
       </c>
       <c r="FL15" t="n">
         <v>-0</v>
@@ -8903,52 +8903,52 @@
         <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
         <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.0001028972701101179</v>
+        <v>0.001446682459579302</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.01271973181703341</v>
+        <v>0.02225167308014944</v>
       </c>
       <c r="FS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.004702515901304995</v>
+        <v>0.03517091653555936</v>
       </c>
       <c r="FU15" t="n">
         <v>-0</v>
       </c>
       <c r="FV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.00474094176887455</v>
+        <v>-0.2253682194634274</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.01259264197697419</v>
+        <v>-0.1234220854923504</v>
       </c>
       <c r="GB15" t="n">
         <v>0</v>
       </c>
       <c r="GC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD15" t="n">
         <v>-0</v>
@@ -8957,7 +8957,7 @@
         <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
         <v>0</v>
@@ -8968,16 +8968,16 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.298089489318609</v>
+        <v>0.155972439565024</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1354294650751428</v>
+        <v>-0.09622256051772876</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -8989,40 +8989,40 @@
         <v>-0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.04364549437033808</v>
+        <v>-0.03886143735322568</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1889463385098223</v>
+        <v>0.2518726040916712</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1825061156211827</v>
+        <v>-0.1285413369900358</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.0541964413404111</v>
+        <v>-0.04370343818059273</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.06376410082296115</v>
+        <v>0.02476678448606879</v>
       </c>
       <c r="U16" t="n">
         <v>-0</v>
@@ -9031,52 +9031,52 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.02380581734686323</v>
+        <v>-0.07196423608037669</v>
       </c>
       <c r="X16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.00893621028586509</v>
+        <v>0.001306561279519546</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.1265645593624711</v>
+        <v>-0.03360975540458343</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.02701925482204472</v>
+        <v>-0.06844559186300758</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>-0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.01474618082267755</v>
+        <v>-0.006029361750864756</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.07125792223437141</v>
+        <v>0.0412640541570007</v>
       </c>
       <c r="AM16" t="n">
         <v>-0</v>
@@ -9085,52 +9085,52 @@
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.01616913186719522</v>
+        <v>-0.02683643536122823</v>
       </c>
       <c r="AP16" t="n">
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS16" t="n">
-        <v>-0.0278797167483417</v>
+        <v>0.002028360372351898</v>
       </c>
       <c r="AT16" t="n">
         <v>-0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.292261113554585</v>
+        <v>0.2333577827622069</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.01760242349176605</v>
+        <v>-0.07286435665859202</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.0265865964931553</v>
+        <v>-0.01009424936304236</v>
       </c>
       <c r="BC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.0241170015159488</v>
+        <v>-0.03309380777990271</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -9139,79 +9139,79 @@
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.1587315168108064</v>
+        <v>-0.05573528281984817</v>
       </c>
       <c r="BH16" t="n">
         <v>0</v>
       </c>
       <c r="BI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ16" t="n">
         <v>-0</v>
       </c>
       <c r="BK16" t="n">
-        <v>-0.0356574522810949</v>
+        <v>-0.01398513874810747</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.04317003238564474</v>
+        <v>0.06484486646354587</v>
       </c>
       <c r="BN16" t="n">
         <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.0782655408176785</v>
+        <v>0.07152655991888596</v>
       </c>
       <c r="BQ16" t="n">
         <v>-0</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>-0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-8.077218504408724e-05</v>
+        <v>0.03308456573248205</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.1714467691970225</v>
+        <v>0.1520665715673633</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.009404745073706493</v>
+        <v>-0.06851541053059443</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB16" t="n">
         <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.01602079042524744</v>
+        <v>-0.01497429356889631</v>
       </c>
       <c r="CD16" t="n">
         <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.05253181223019728</v>
+        <v>-0.05178257164841815</v>
       </c>
       <c r="CF16" t="n">
         <v>-0</v>
@@ -9220,25 +9220,25 @@
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.01489686064762871</v>
+        <v>0.03377500985029033</v>
       </c>
       <c r="CI16" t="n">
         <v>-0</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>0.0146183041565796</v>
+        <v>0.02116481628769542</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.05806465670580274</v>
+        <v>-0.117737890531117</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
@@ -9247,10 +9247,10 @@
         <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.02076693377692065</v>
+        <v>0.03423411529435206</v>
       </c>
       <c r="CR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS16" t="n">
         <v>-0</v>
@@ -9259,13 +9259,13 @@
         <v>-0</v>
       </c>
       <c r="CU16" t="n">
-        <v>-0.02846159305678699</v>
+        <v>0.0005398387182931385</v>
       </c>
       <c r="CV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.03788718687649849</v>
+        <v>-0.04772034610442165</v>
       </c>
       <c r="CX16" t="n">
         <v>0</v>
@@ -9274,7 +9274,7 @@
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.005566995344276616</v>
+        <v>0.01851440728067023</v>
       </c>
       <c r="DA16" t="n">
         <v>0</v>
@@ -9286,13 +9286,13 @@
         <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.02213407542598488</v>
+        <v>0.01547047884752793</v>
       </c>
       <c r="DE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.04733185053257771</v>
+        <v>-0.005765712141132543</v>
       </c>
       <c r="DG16" t="n">
         <v>-0</v>
@@ -9301,7 +9301,7 @@
         <v>-0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.06293929450548898</v>
+        <v>-0.03682887492613426</v>
       </c>
       <c r="DJ16" t="n">
         <v>0</v>
@@ -9313,121 +9313,121 @@
         <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>-0.02513463921775738</v>
+        <v>-0.01917922191266397</v>
       </c>
       <c r="DN16" t="n">
         <v>-0</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.005048494911745488</v>
+        <v>-0.02783229063230527</v>
       </c>
       <c r="DP16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>-0.0120660522560462</v>
+        <v>0.01953283401640284</v>
       </c>
       <c r="DS16" t="n">
         <v>-0</v>
       </c>
       <c r="DT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>-0.02753150294405674</v>
+        <v>-0.009439757766637715</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.03543987838714583</v>
+        <v>0.05891236855715742</v>
       </c>
       <c r="DY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ16" t="n">
         <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.03553913614500354</v>
+        <v>-0.01364215096217806</v>
       </c>
       <c r="EB16" t="n">
         <v>0</v>
       </c>
       <c r="EC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>-0.00389983293429174</v>
+        <v>0.01819473538556573</v>
       </c>
       <c r="EF16" t="n">
         <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.01677086699223626</v>
+        <v>-0.0118767991945741</v>
       </c>
       <c r="EH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI16" t="n">
         <v>0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.04077756089304283</v>
+        <v>0.0006649498553958761</v>
       </c>
       <c r="EK16" t="n">
         <v>-0</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
         <v>0</v>
       </c>
       <c r="EN16" t="n">
-        <v>0.03414238126307257</v>
+        <v>0.02667780111119892</v>
       </c>
       <c r="EO16" t="n">
         <v>0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.04253841965994799</v>
+        <v>0.002572209961813239</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
         <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.00399640592548153</v>
+        <v>-0.01880645116802019</v>
       </c>
       <c r="ET16" t="n">
         <v>-0</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
         <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0.03312829650822156</v>
+        <v>-0.01174294857124661</v>
       </c>
       <c r="EX16" t="n">
         <v>0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.05108021272304407</v>
+        <v>-0.05912776656897611</v>
       </c>
       <c r="EZ16" t="n">
         <v>-0</v>
@@ -9436,52 +9436,52 @@
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.004538700633810942</v>
+        <v>0.01042047738727457</v>
       </c>
       <c r="FC16" t="n">
         <v>-0</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
         <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.01307609295759565</v>
+        <v>0.02077758611580128</v>
       </c>
       <c r="FG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.03038568942240352</v>
+        <v>-0.03041500132227</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.03112153645513354</v>
+        <v>0.04191550815688255</v>
       </c>
       <c r="FL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO16" t="n">
-        <v>0.001473710445730056</v>
+        <v>0.003211193203461712</v>
       </c>
       <c r="FP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.0003192868229813104</v>
+        <v>-0.000769339971091427</v>
       </c>
       <c r="FR16" t="n">
         <v>-0</v>
@@ -9490,7 +9490,7 @@
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.0003966508852620474</v>
+        <v>0.00142752537370704</v>
       </c>
       <c r="FU16" t="n">
         <v>0</v>
@@ -9502,13 +9502,13 @@
         <v>-0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0.009180574190004049</v>
+        <v>0.02185178455127406</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.04586158199090658</v>
+        <v>-0.03179108699746683</v>
       </c>
       <c r="GA16" t="n">
         <v>0</v>
@@ -9517,63 +9517,63 @@
         <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG16" t="n">
-        <v>0.006595918572033141</v>
+        <v>0.00347951169891702</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0.1338348978261612</v>
+        <v>-0.04217341049326683</v>
       </c>
       <c r="B17" t="n">
-        <v>0.08263894845971984</v>
+        <v>0.05847934833850049</v>
       </c>
       <c r="C17" t="n">
         <v>-0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.01154699669892753</v>
+        <v>-0.03077712005754459</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.08444415598751591</v>
+        <v>-0.03174067779331156</v>
       </c>
       <c r="K17" t="n">
-        <v>0.07361351381067802</v>
+        <v>0.09594282640354122</v>
       </c>
       <c r="L17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1202295641571193</v>
+        <v>-0.03650990885445582</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9585,106 +9585,106 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.01066840327067597</v>
+        <v>0.01215925758517134</v>
       </c>
       <c r="T17" t="n">
-        <v>0.07335312673787615</v>
+        <v>0.0165835895490681</v>
       </c>
       <c r="U17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.105302223934785</v>
+        <v>0.009693288571757549</v>
       </c>
       <c r="X17" t="n">
         <v>-0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.04000092375131312</v>
+        <v>0.000254856096445109</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.1311781051572902</v>
+        <v>-0.01033680870339855</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.05008256604567302</v>
+        <v>-0.02753142339956939</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>-0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>-0.01147586378543222</v>
+        <v>-0.004182452187162158</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.02524903747548366</v>
+        <v>0.02044789636088457</v>
       </c>
       <c r="AM17" t="n">
         <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.03547707329638132</v>
+        <v>-0.01085208457079747</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS17" t="n">
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0.02088942516082826</v>
+        <v>-0.01077312931224502</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.1686198193492331</v>
+        <v>0.05826760780787705</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
       </c>
       <c r="AW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.2198607508625486</v>
+        <v>-0.02183784997912451</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
         <v>-0</v>
@@ -9696,10 +9696,10 @@
         <v>-0</v>
       </c>
       <c r="BC17" t="n">
-        <v>-0.04279524592258969</v>
+        <v>-0.02393367409578731</v>
       </c>
       <c r="BD17" t="n">
-        <v>-0.01101905933117242</v>
+        <v>0.01303070650114085</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -9708,40 +9708,40 @@
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.1370147441331965</v>
+        <v>-0.02499307477548433</v>
       </c>
       <c r="BH17" t="n">
         <v>0</v>
       </c>
       <c r="BI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ17" t="n">
         <v>0</v>
       </c>
       <c r="BK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0.03804444172611849</v>
+        <v>0.003828641250506354</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.04864576759465348</v>
+        <v>0.01669937715265024</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
         <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.07978456692799515</v>
+        <v>0.02954137345355941</v>
       </c>
       <c r="BQ17" t="n">
         <v>-0</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>-0</v>
@@ -9750,37 +9750,37 @@
         <v>-0</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.006066807748124372</v>
+        <v>0.006197331233334059</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.08840306755869493</v>
+        <v>0.05858150080079883</v>
       </c>
       <c r="BW17" t="n">
         <v>-0</v>
       </c>
       <c r="BX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.07905192921183499</v>
+        <v>-0.006039296210371884</v>
       </c>
       <c r="BZ17" t="n">
         <v>-0</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.02716864490401043</v>
+        <v>0.01368325367531123</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.01089520915294411</v>
+        <v>-0.01436112570492145</v>
       </c>
       <c r="CF17" t="n">
         <v>-0</v>
@@ -9789,10 +9789,10 @@
         <v>0</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.009448706022791208</v>
+        <v>0.007661216208070533</v>
       </c>
       <c r="CI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ17" t="n">
         <v>-0</v>
@@ -9804,10 +9804,10 @@
         <v>-0</v>
       </c>
       <c r="CM17" t="n">
-        <v>-0.03708420063936621</v>
+        <v>-0.01514815915781622</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.07928632718024156</v>
+        <v>-0.05700577979241748</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
@@ -9816,52 +9816,52 @@
         <v>0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.08621854434735013</v>
+        <v>0.02459604937108281</v>
       </c>
       <c r="CR17" t="n">
         <v>-0</v>
       </c>
       <c r="CS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT17" t="n">
         <v>-0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
-        <v>0.0160188097356615</v>
+        <v>0.01145582617907311</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.002319532205424769</v>
+        <v>-0.01617693790372076</v>
       </c>
       <c r="CX17" t="n">
         <v>0</v>
       </c>
       <c r="CY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.006136856092353616</v>
+        <v>0.001883483305134006</v>
       </c>
       <c r="DA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB17" t="n">
         <v>0</v>
       </c>
       <c r="DC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD17" t="n">
         <v>0</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.04732419591393504</v>
+        <v>0.01026268722053705</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.09233885632789048</v>
+        <v>-0.04454159183815044</v>
       </c>
       <c r="DG17" t="n">
         <v>-0</v>
@@ -9870,25 +9870,25 @@
         <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.001716176709267077</v>
+        <v>-0.001043911069646663</v>
       </c>
       <c r="DJ17" t="n">
         <v>0</v>
       </c>
       <c r="DK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.03926442950834368</v>
+        <v>0.007411374081207241</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.01782732862654791</v>
+        <v>-0.002547881895423345</v>
       </c>
       <c r="DP17" t="n">
         <v>-0</v>
@@ -9897,13 +9897,13 @@
         <v>-0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.08345842215410899</v>
+        <v>-0.007633748711798573</v>
       </c>
       <c r="DS17" t="n">
         <v>-0</v>
       </c>
       <c r="DT17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU17" t="n">
         <v>-0</v>
@@ -9912,10 +9912,10 @@
         <v>-0</v>
       </c>
       <c r="DW17" t="n">
-        <v>-0.01312801518793354</v>
+        <v>0.01193786613411172</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.02986044600754936</v>
+        <v>0.02407613535372248</v>
       </c>
       <c r="DY17" t="n">
         <v>0</v>
@@ -9924,25 +9924,25 @@
         <v>0</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.002060045468957204</v>
+        <v>-0.007058258186539629</v>
       </c>
       <c r="EB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC17" t="n">
         <v>-0</v>
       </c>
       <c r="ED17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE17" t="n">
         <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>-0.01749742304653857</v>
+        <v>-0.003327325623257766</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.05020283518573707</v>
+        <v>0.0012316720284549</v>
       </c>
       <c r="EH17" t="n">
         <v>-0</v>
@@ -9951,13 +9951,13 @@
         <v>0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>-0.005245538400809677</v>
+        <v>0.004767600703451826</v>
       </c>
       <c r="EK17" t="n">
         <v>-0</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
         <v>-0</v>
@@ -9966,46 +9966,46 @@
         <v>-0</v>
       </c>
       <c r="EO17" t="n">
-        <v>-0.006678501024510885</v>
+        <v>0.002446771392937458</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.05934440909241838</v>
+        <v>-0.01145702439549684</v>
       </c>
       <c r="EQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER17" t="n">
         <v>0</v>
       </c>
       <c r="ES17" t="n">
-        <v>-0.001052149874898258</v>
+        <v>-0.01045829200154164</v>
       </c>
       <c r="ET17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW17" t="n">
         <v>0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0.02159097708579868</v>
+        <v>0.01306633766681252</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.01658425744736751</v>
+        <v>-0.021181062805254</v>
       </c>
       <c r="EZ17" t="n">
         <v>-0</v>
       </c>
       <c r="FA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>-0.01784032160685237</v>
+        <v>0.002850029668985397</v>
       </c>
       <c r="FC17" t="n">
         <v>-0</v>
@@ -10020,37 +10020,37 @@
         <v>-0</v>
       </c>
       <c r="FG17" t="n">
-        <v>0.03439140214710651</v>
+        <v>0.00616934488287291</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.03463281537546917</v>
+        <v>-0.0009867513752085568</v>
       </c>
       <c r="FI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ17" t="n">
         <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.07943901003356045</v>
+        <v>0.01771351767522171</v>
       </c>
       <c r="FL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO17" t="n">
         <v>-0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.07400196149409533</v>
+        <v>-0.004525894736123406</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.01319962537667771</v>
+        <v>0.003191914593556213</v>
       </c>
       <c r="FR17" t="n">
         <v>0</v>
@@ -10059,7 +10059,7 @@
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>-0.004024545422736414</v>
+        <v>0.002931511340561417</v>
       </c>
       <c r="FU17" t="n">
         <v>-0</v>
@@ -10068,16 +10068,16 @@
         <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
         <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>0.01480819807646421</v>
+        <v>0.00302114032582686</v>
       </c>
       <c r="FZ17" t="n">
-        <v>-0.04855946916133372</v>
+        <v>-0.01434701244174842</v>
       </c>
       <c r="GA17" t="n">
         <v>-0</v>
@@ -10086,13 +10086,13 @@
         <v>-0</v>
       </c>
       <c r="GC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF17" t="n">
         <v>-0</v>
